--- a/output/pdf_financials_xlsx/VRTX.xlsx
+++ b/output/pdf_financials_xlsx/VRTX.xlsx
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.924716</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.572739</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.972014</v>
       </c>
     </row>
     <row r="93">
@@ -3204,7 +3204,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.924716</v>
       </c>

--- a/output/pdf_financials_xlsx/VRTX.xlsx
+++ b/output/pdf_financials_xlsx/VRTX.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.99447</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.183968</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.411797</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.271711</v>
+        <v>4.266181</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-0.143949</v>
+        <v>3.040019</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.411797</v>
       </c>
     </row>
     <row r="37">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.398698</v>
+        <v>0.404228</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.34225</v>
+        <v>0.158282</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.703928</v>
+        <v>0.292131</v>
       </c>
     </row>
     <row r="49">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/VRTX.xlsx
+++ b/output/pdf_financials_xlsx/VRTX.xlsx
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -6230,7 +6230,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -6821,7 +6825,11 @@
           <t>Purchase of marketable securities (Note 5)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>-0.2</v>
       </c>
@@ -6918,7 +6926,11 @@
           <t>Proceeds from share issuances (Note 9)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
         <v>3.862</v>
       </c>
